--- a/templates/contoh-proyek-dari-excel.xlsx
+++ b/templates/contoh-proyek-dari-excel.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -579,6 +579,21 @@
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Opsional, 1–10 (default 3). PIC tetap dapat menambah putaran.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>data_uji_coba_mulai_putaran</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Opsional. Putaran pertama panelis melihat data uji coba butir (0 = tidak ditampilkan; bawaan 2 = setelah hasil Putaran 1).</t>
         </is>
       </c>
     </row>
@@ -593,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -602,6 +617,9 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="90" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -635,11 +653,26 @@
           <t>rubrik</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>kunci_jawaban</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>p_uji_coba</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>n_uji_coba</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>BIO-001</t>
+          <t>BIO-101</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -661,11 +694,22 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>BIO-002</t>
+          <t>BIO-102</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -687,11 +731,22 @@
         <v>1</v>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>BIO-003</t>
+          <t>BIO-103</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -706,22 +761,33 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>PG Kompleks</t>
+          <t>PG Kompleks MCMA</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0: tidak ada pernyataan tepat | 1: 1 pernyataan tepat | 2: semua 2 pernyataan tepat</t>
-        </is>
+          <t>Skor = banyak opsi A–E yang sesuai kunci (opsi benar dipilih, opsi salah tidak dipilih)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>B, E</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>BIO-004</t>
+          <t>BIO-104</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -743,11 +809,22 @@
         <v>1</v>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>BIO-005</t>
+          <t>BIO-105</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -762,22 +839,33 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>PG Kompleks</t>
+          <t>PG Kompleks MCMA</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0: tidak ada pernyataan tepat | 1: 1 pernyataan tepat | 2: 2 pernyataan tepat | 3: semua 3 pernyataan tepat</t>
-        </is>
+          <t>Skor = banyak opsi A–E yang sesuai kunci (opsi benar dipilih, opsi salah tidak dipilih)</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>A, B, D</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>BIO-006</t>
+          <t>BIO-106</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -799,11 +887,22 @@
         <v>1</v>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>BIO-007</t>
+          <t>BIO-107</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -825,11 +924,22 @@
         <v>1</v>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>BIO-008</t>
+          <t>BIO-108</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -851,11 +961,22 @@
         <v>1</v>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>BIO-009</t>
+          <t>BIO-109</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -877,11 +998,22 @@
         <v>1</v>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>BIO-010</t>
+          <t>BIO-110</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -896,7 +1028,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>PG Kompleks Benar-Salah</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -904,14 +1036,25 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0: tidak menjawab/salah | 1: menjawab sebagian kecil | 2: menjawab lengkap dan tepat</t>
-        </is>
+          <t>0: 0 pernyataan tepat | 1: 1 pernyataan tepat | 2: 2 pernyataan tepat</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>(1) Salah · (2) Benar</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>FIS-001</t>
+          <t>FIS-101</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -933,11 +1076,22 @@
         <v>1</v>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>FIS-002</t>
+          <t>FIS-102</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -959,11 +1113,22 @@
         <v>1</v>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>FIS-003</t>
+          <t>FIS-103</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -978,22 +1143,33 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>PG Kompleks</t>
+          <t>PG Kompleks MCMA</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0: tidak ada pernyataan tepat | 1: 1 pernyataan tepat | 2: semua 2 pernyataan tepat</t>
-        </is>
+          <t>Skor = banyak opsi A–E yang sesuai kunci (opsi benar dipilih, opsi salah tidak dipilih)</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>B, E</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>FIS-004</t>
+          <t>FIS-104</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1015,11 +1191,22 @@
         <v>1</v>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>FIS-005</t>
+          <t>FIS-105</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1034,22 +1221,33 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>PG Kompleks</t>
+          <t>PG Kompleks MCMA</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0: tidak ada pernyataan tepat | 1: 1 pernyataan tepat | 2: 2 pernyataan tepat | 3: semua 3 pernyataan tepat</t>
-        </is>
+          <t>Skor = banyak opsi A–E yang sesuai kunci (opsi benar dipilih, opsi salah tidak dipilih)</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>A, B, D</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>FIS-006</t>
+          <t>FIS-106</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1071,11 +1269,22 @@
         <v>1</v>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>FIS-007</t>
+          <t>FIS-107</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1097,11 +1306,22 @@
         <v>1</v>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>FIS-008</t>
+          <t>FIS-108</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1123,11 +1343,22 @@
         <v>1</v>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>FIS-009</t>
+          <t>FIS-109</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1149,11 +1380,22 @@
         <v>1</v>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>FIS-010</t>
+          <t>FIS-110</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1168,7 +1410,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>PG Kompleks Benar-Salah</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
@@ -1176,8 +1418,19 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0: tidak menjawab/salah | 1: menjawab sebagian kecil | 2: menjawab lengkap dan tepat</t>
-        </is>
+          <t>0: 0 pernyataan tepat | 1: 1 pernyataan tepat | 2: 2 pernyataan tepat</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>(1) Salah · (2) Benar</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1200</v>
       </c>
     </row>
   </sheetData>
@@ -1530,7 +1783,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Butir: id_butir unik, kode_mapel, nama_mapel, bentuk_soal (PG / PG Kompleks / Essay), skor_maks (PG = 1), rubrik dipisah tanda | (boleh kosong). Butir masuk bank sekaligus dialokasikan ke mapel proyek.</t>
+          <t>Butir: id_butir unik, kode_mapel, nama_mapel, bentuk_soal (PG = pilihan ganda biasa A–E / PG Kompleks MCMA = jawaban benar lebih dari 1 / PG Kompleks Benar-Salah), skor_maks (PG = 1; MCMA = banyak opsi, umumnya 5, karena skor = banyak opsi yang sesuai kunci, contoh kunci ABC dan jawaban ABD → 3; Benar-Salah = banyak pernyataan), rubrik dipisah tanda | (boleh kosong), kunci_jawaban (ditampilkan kepada panelis pada setiap butir; PG: huruf opsi, MCMA: daftar opsi benar, Benar-Salah: per pernyataan). Kolom opsional p_uji_coba = tingkat kesulitan butir dari uji coba (rata-rata skor ÷ skor maks; PG = proporsi menjawab benar), boleh 0,58 atau 58%, dan n_uji_coba = jumlah peserta uji coba; ditampilkan ke panelis mulai putaran yang diatur. Essay tidak dipakai. Butir masuk bank sekaligus dialokasikan ke mapel proyek.</t>
         </is>
       </c>
     </row>

--- a/templates/contoh-proyek-dari-excel.xlsx
+++ b/templates/contoh-proyek-dari-excel.xlsx
@@ -77,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -94,6 +94,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -585,15 +586,15 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>data_uji_coba_mulai_putaran</t>
+          <t>kategori_bank_soal_mulai_putaran</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Opsional. Putaran pertama panelis melihat data uji coba butir (0 = tidak ditampilkan; bawaan 2 = setelah hasil Putaran 1).</t>
+          <t>Opsional. Kategori bank soal (kategori + measure) tampil ke panelis mulai putaran ini; 1 = sejak Putaran 1 (bawaan), 0 = tidak ditampilkan.</t>
         </is>
       </c>
     </row>
@@ -660,12 +661,12 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>p_uji_coba</t>
+          <t>measure</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>n_uji_coba</t>
+          <t>kategori</t>
         </is>
       </c>
     </row>
@@ -699,11 +700,13 @@
           <t>B</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1200</v>
+      <c r="H2" s="6" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Mudah</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -736,11 +739,13 @@
           <t>E</t>
         </is>
       </c>
-      <c r="H3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1200</v>
+      <c r="H3" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Mudah</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -777,11 +782,13 @@
           <t>B, E</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1200</v>
+      <c r="H4" s="6" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sangat mudah</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -814,11 +821,13 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1200</v>
+      <c r="H5" s="6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sangat sulit</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -855,11 +864,13 @@
           <t>A, B, D</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1200</v>
+      <c r="H6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sangat sulit</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -892,11 +903,13 @@
           <t>B</t>
         </is>
       </c>
-      <c r="H7" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1200</v>
+      <c r="H7" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sulit</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -929,11 +942,13 @@
           <t>E</t>
         </is>
       </c>
-      <c r="H8" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1200</v>
+      <c r="H8" s="6" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Mudah</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -966,11 +981,13 @@
           <t>C</t>
         </is>
       </c>
-      <c r="H9" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1200</v>
+      <c r="H9" s="6" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sangat mudah</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1003,11 +1020,13 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H10" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1200</v>
+      <c r="H10" s="6" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Sangat mudah</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1044,11 +1063,13 @@
           <t>(1) Salah · (2) Benar</t>
         </is>
       </c>
-      <c r="H11" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1200</v>
+      <c r="H11" s="6" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Sangat mudah</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1081,11 +1102,13 @@
           <t>B</t>
         </is>
       </c>
-      <c r="H12" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1200</v>
+      <c r="H12" s="6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Sangat sulit</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1118,11 +1141,13 @@
           <t>E</t>
         </is>
       </c>
-      <c r="H13" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1200</v>
+      <c r="H13" s="6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Sangat sulit</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1159,11 +1184,13 @@
           <t>B, E</t>
         </is>
       </c>
-      <c r="H14" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1200</v>
+      <c r="H14" s="6" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Sulit</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1196,11 +1223,13 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H15" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1200</v>
+      <c r="H15" s="6" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Mudah</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1237,11 +1266,13 @@
           <t>A, B, D</t>
         </is>
       </c>
-      <c r="H16" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1200</v>
+      <c r="H16" s="6" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Sangat mudah</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1274,11 +1305,13 @@
           <t>B</t>
         </is>
       </c>
-      <c r="H17" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1200</v>
+      <c r="H17" s="6" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Sangat mudah</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1311,11 +1344,13 @@
           <t>E</t>
         </is>
       </c>
-      <c r="H18" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1200</v>
+      <c r="H18" s="6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Sangat sulit</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1348,11 +1383,13 @@
           <t>C</t>
         </is>
       </c>
-      <c r="H19" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1200</v>
+      <c r="H19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Sangat sulit</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1385,11 +1422,13 @@
           <t>A</t>
         </is>
       </c>
-      <c r="H20" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1200</v>
+      <c r="H20" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Sulit</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1426,11 +1465,13 @@
           <t>(1) Salah · (2) Benar</t>
         </is>
       </c>
-      <c r="H21" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1200</v>
+      <c r="H21" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Sulit</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1783,7 +1824,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Butir: id_butir unik, kode_mapel, nama_mapel, bentuk_soal (PG = pilihan ganda biasa A–E / PG Kompleks MCMA = jawaban benar lebih dari 1 / PG Kompleks Benar-Salah), skor_maks (PG = 1; MCMA = banyak opsi, umumnya 5, karena skor = banyak opsi yang sesuai kunci, contoh kunci ABC dan jawaban ABD → 3; Benar-Salah = banyak pernyataan), rubrik dipisah tanda | (boleh kosong), kunci_jawaban (ditampilkan kepada panelis pada setiap butir; PG: huruf opsi, MCMA: daftar opsi benar, Benar-Salah: per pernyataan). Kolom opsional p_uji_coba = tingkat kesulitan butir dari uji coba (rata-rata skor ÷ skor maks; PG = proporsi menjawab benar), boleh 0,58 atau 58%, dan n_uji_coba = jumlah peserta uji coba; ditampilkan ke panelis mulai putaran yang diatur. Essay tidak dipakai. Butir masuk bank sekaligus dialokasikan ke mapel proyek.</t>
+          <t>Butir: id_butir unik, kode_mapel, nama_mapel, bentuk_soal (PG = pilihan ganda biasa A–E / PG Kompleks MCMA = jawaban benar lebih dari 1 / PG Kompleks Benar-Salah), skor_maks (PG = 1; MCMA = banyak opsi, umumnya 5, karena skor = banyak opsi yang sesuai kunci, contoh kunci ABC dan jawaban ABD → 3; Benar-Salah = banyak pernyataan), rubrik dipisah tanda | (boleh kosong), kunci_jawaban (ditampilkan kepada panelis pada setiap butir; PG: huruf opsi, MCMA: daftar opsi benar, Benar-Salah: per pernyataan). Kolom opsional measure (mis. logit Rasch, boleh desimal koma) dan kategori (Sangat mudah / Mudah / Sulit / Sangat sulit; relatif terhadap M ± 1SD measure seluruh butir) diisi bersamaan; ditampilkan ke panelis sejak Putaran 1 (diatur di sheet Proyek). Essay tidak dipakai. Butir masuk bank sekaligus dialokasikan ke mapel proyek.</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1838,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Username boleh diisi atau dikosongkan (otomatis). Password awal tidak ada di file: aplikasi membuatnya acak dan menampilkannya sekali untuk diunduh (CSV).</t>
+          <t>Username boleh diisi atau dikosongkan (otomatis). Password tidak ada di file: semua akun baru memakai password default dari aplikasi dan wajib menggantinya saat login pertama.</t>
         </is>
       </c>
     </row>

--- a/templates/contoh-proyek-dari-excel.xlsx
+++ b/templates/contoh-proyek-dari-excel.xlsx
@@ -774,12 +774,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Skor = banyak opsi A–E yang sesuai kunci (opsi benar dipilih, opsi salah tidak dipilih)</t>
+          <t>0: 0 poin | 1: 1 poin | 2: 2 poin | 3: 3 poin | 4: 4 poin | 5: 5 poin</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>B, E</t>
+          <t>B,E</t>
         </is>
       </c>
       <c r="H4" s="6" t="n">
@@ -856,12 +856,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Skor = banyak opsi A–E yang sesuai kunci (opsi benar dipilih, opsi salah tidak dipilih)</t>
+          <t>0: 0 poin | 1: 1 poin | 2: 2 poin | 3: 3 poin | 4: 4 poin | 5: 5 poin</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>A, B, D</t>
+          <t>A,B,D</t>
         </is>
       </c>
       <c r="H6" s="6" t="n">
@@ -1051,16 +1051,16 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0: 0 pernyataan tepat | 1: 1 pernyataan tepat | 2: 2 pernyataan tepat</t>
+          <t>0: 0 poin | 1: 1 poin | 2: 2 poin | 3: 3 poin | 4: 4 poin | 5: 5 poin</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>(1) Salah · (2) Benar</t>
+          <t>BSBSB</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Skor = banyak opsi A–E yang sesuai kunci (opsi benar dipilih, opsi salah tidak dipilih)</t>
+          <t>0: 0 poin | 1: 1 poin | 2: 2 poin | 3: 3 poin | 4: 4 poin | 5: 5 poin</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>B, E</t>
+          <t>B,E</t>
         </is>
       </c>
       <c r="H14" s="6" t="n">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Skor = banyak opsi A–E yang sesuai kunci (opsi benar dipilih, opsi salah tidak dipilih)</t>
+          <t>0: 0 poin | 1: 1 poin | 2: 2 poin | 3: 3 poin | 4: 4 poin | 5: 5 poin</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>A, B, D</t>
+          <t>A,B,D</t>
         </is>
       </c>
       <c r="H16" s="6" t="n">
@@ -1453,16 +1453,16 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0: 0 pernyataan tepat | 1: 1 pernyataan tepat | 2: 2 pernyataan tepat</t>
+          <t>0: 0 poin | 1: 1 poin | 2: 2 poin | 3: 3 poin | 4: 4 poin | 5: 5 poin</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>(1) Salah · (2) Benar</t>
+          <t>BBSBS</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
@@ -1824,7 +1824,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Butir: id_butir unik, kode_mapel, nama_mapel, bentuk_soal (PG = pilihan ganda biasa A–E / PG Kompleks MCMA = jawaban benar lebih dari 1 / PG Kompleks Benar-Salah), skor_maks (PG = 1; MCMA = banyak opsi, umumnya 5, karena skor = banyak opsi yang sesuai kunci, contoh kunci ABC dan jawaban ABD → 3; Benar-Salah = banyak pernyataan), rubrik dipisah tanda | (boleh kosong), kunci_jawaban (ditampilkan kepada panelis pada setiap butir; PG: huruf opsi, MCMA: daftar opsi benar, Benar-Salah: per pernyataan). Kolom opsional measure (mis. logit Rasch, boleh desimal koma) dan kategori (Sangat mudah / Mudah / Sulit / Sangat sulit; relatif terhadap M ± 1SD measure seluruh butir) diisi bersamaan; ditampilkan ke panelis sejak Putaran 1 (diatur di sheet Proyek). Essay tidak dipakai. Butir masuk bank sekaligus dialokasikan ke mapel proyek.</t>
+          <t>Butir: id_butir unik, kode_mapel, nama_mapel, bentuk_soal (PG = pilihan ganda biasa A–E / PG Kompleks MCMA = jawaban benar lebih dari 1 / PG Kompleks Benar-Salah / Essay), skor_maks (otomatis: PG 1, MCMA 5 karena 5 opsi, Benar-Salah 5 karena 5 pernyataan, Essay 2 dengan rubrik 0–1–2), rubrik dipisah tanda | (boleh kosong), kunci_jawaban (ditampilkan kepada panelis pada setiap butir; PG: satu huruf opsi, mis. E; MCMA: huruf opsi yang benar dipisah koma, mis. A,C,D; Benar-Salah: B atau S untuk pernyataan 1–5 berurutan, mis. BSBSB; Essay: pedoman jawaban). Kolom opsional measure (mis. logit Rasch, boleh desimal koma) dan kategori (Sangat mudah / Mudah / Sulit / Sangat sulit; relatif terhadap M ± 1SD measure seluruh butir) diisi bersamaan; ditampilkan ke panelis sejak Putaran 1 (diatur di sheet Proyek). Butir masuk bank sekaligus dialokasikan ke mapel proyek.</t>
         </is>
       </c>
     </row>
